--- a/plans/KPBot-Knowledge-工作拆分与人力评估.xlsx
+++ b/plans/KPBot-Knowledge-工作拆分与人力评估.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务拆分" sheetId="1" r:id="Re397c24a436a44f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务拆分" sheetId="1" r:id="Rd548e2b38a7d4ebd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -514,10 +514,10 @@
         <x:v>I01-02</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
-        <x:v>让 knowledge-update Skill 调用三类内置制作工具</x:v>
+        <x:v>让 knowledge-create 与 knowledge-update Skill 分别调用三类内置制作工具</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>新增或变更来源可从统一更新入口生成对应 Wiki 产物仓</x:v>
+        <x:v>新增来源由 create 生成首版，来源变化由 update 刷新对应 Wiki 产物仓</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
         <x:v>I01-01</x:v>
@@ -1427,7 +1427,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4026030c41784b68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46061ecd9ff343cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>